--- a/Team-Data/2008-09/1-17-2008-09.xlsx
+++ b/Team-Data/2008-09/1-17-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,28 +806,28 @@
         <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AF2" t="n">
         <v>10</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -778,16 +845,16 @@
         <v>16</v>
       </c>
       <c r="AQ2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR2" t="n">
         <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>9</v>
@@ -808,10 +875,10 @@
         <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -858,49 +925,49 @@
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.481</v>
+        <v>0.479</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="M3" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.378</v>
+        <v>0.373</v>
       </c>
       <c r="O3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="P3" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.768</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
         <v>16.1</v>
       </c>
       <c r="W3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X3" t="n">
         <v>5</v>
@@ -909,22 +976,22 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -936,7 +1003,7 @@
         <v>12</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -945,13 +1012,13 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
@@ -960,7 +1027,7 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -981,7 +1048,7 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -990,7 +1057,7 @@
         <v>26</v>
       </c>
       <c r="BA3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1025,97 +1092,97 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4</v>
+        <v>0.385</v>
       </c>
       <c r="H4" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J4" t="n">
-        <v>75.7</v>
+        <v>75.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>5.3</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O4" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P4" t="n">
-        <v>24.9</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="T4" t="n">
-        <v>39</v>
+        <v>38.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V4" t="n">
         <v>15.5</v>
       </c>
       <c r="W4" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y4" t="n">
         <v>6</v>
       </c>
       <c r="Z4" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG4" t="n">
         <v>22</v>
       </c>
-      <c r="AA4" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>91.40000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>20</v>
-      </c>
       <c r="AH4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1136,7 +1203,7 @@
         <v>19</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>14</v>
@@ -1145,22 +1212,22 @@
         <v>24</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS4" t="n">
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AU4" t="n">
         <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1172,13 +1239,13 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1210,25 +1277,25 @@
         <v>40</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="n">
-        <v>0.425</v>
+        <v>0.45</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
         <v>6.3</v>
@@ -1237,61 +1304,61 @@
         <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8</v>
+        <v>0.797</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
@@ -1300,13 +1367,13 @@
         <v>7</v>
       </c>
       <c r="AI5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>19</v>
@@ -1318,10 +1385,10 @@
         <v>7</v>
       </c>
       <c r="AO5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AP5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,34 +1397,34 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ5" t="n">
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
         <v>22</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1389,49 +1456,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.838</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R6" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
@@ -1440,34 +1507,34 @@
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.4</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
@@ -1491,25 +1558,25 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AM6" t="n">
         <v>7</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AR6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1530,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1571,64 +1638,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F7" t="n">
         <v>17</v>
       </c>
       <c r="G7" t="n">
-        <v>0.575</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
       </c>
       <c r="I7" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J7" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.453</v>
+        <v>0.451</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="N7" t="n">
         <v>0.333</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S7" t="n">
-        <v>32.3</v>
+        <v>32.4</v>
       </c>
       <c r="T7" t="n">
         <v>44.1</v>
       </c>
       <c r="U7" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V7" t="n">
         <v>13.4</v>
       </c>
       <c r="W7" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="X7" t="n">
         <v>5.5</v>
@@ -1637,31 +1704,31 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>99.7</v>
+        <v>99.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE7" t="n">
         <v>12</v>
       </c>
-      <c r="AE7" t="n">
-        <v>11</v>
-      </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1682,31 +1749,31 @@
         <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
       </c>
       <c r="AQ7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS7" t="n">
         <v>3</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
         <v>8</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1753,28 +1820,28 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="n">
         <v>27</v>
       </c>
       <c r="F8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.659</v>
+        <v>0.675</v>
       </c>
       <c r="H8" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J8" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.468</v>
+        <v>0.471</v>
       </c>
       <c r="L8" t="n">
         <v>6.8</v>
@@ -1783,37 +1850,37 @@
         <v>18</v>
       </c>
       <c r="N8" t="n">
-        <v>0.376</v>
+        <v>0.377</v>
       </c>
       <c r="O8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="P8" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.757</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
         <v>30.6</v>
       </c>
       <c r="T8" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U8" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y8" t="n">
         <v>5.8</v>
@@ -1822,34 +1889,34 @@
         <v>22.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.8</v>
+        <v>104.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
       </c>
       <c r="AF8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH8" t="n">
         <v>21</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,7 +1937,7 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR8" t="n">
         <v>24</v>
@@ -1879,16 +1946,16 @@
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AW8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>5</v>
@@ -1900,13 +1967,13 @@
         <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E9" t="n">
         <v>22</v>
       </c>
       <c r="F9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,88 +2020,88 @@
         <v>35.8</v>
       </c>
       <c r="J9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.451</v>
+        <v>0.452</v>
       </c>
       <c r="L9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="M9" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.345</v>
       </c>
       <c r="O9" t="n">
-        <v>16.9</v>
+        <v>17.2</v>
       </c>
       <c r="P9" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.741</v>
+        <v>0.744</v>
       </c>
       <c r="R9" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="S9" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T9" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U9" t="n">
         <v>20.1</v>
       </c>
       <c r="V9" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="W9" t="n">
         <v>6.7</v>
       </c>
       <c r="X9" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y9" t="n">
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.40000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG9" t="n">
         <v>13</v>
       </c>
-      <c r="AF9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14</v>
-      </c>
       <c r="AH9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI9" t="n">
         <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2046,7 +2113,7 @@
         <v>23</v>
       </c>
       <c r="AO9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP9" t="n">
         <v>25</v>
@@ -2055,13 +2122,13 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
         <v>21</v>
@@ -2070,22 +2137,22 @@
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2286,7 @@
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>14</v>
@@ -2234,13 +2301,13 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT10" t="n">
         <v>8</v>
@@ -2252,13 +2319,13 @@
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>16</v>
       </c>
       <c r="G11" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="H11" t="n">
         <v>48.4</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>34.9</v>
       </c>
       <c r="J11" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="L11" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="O11" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P11" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="S11" t="n">
-        <v>32.3</v>
+        <v>32.2</v>
       </c>
       <c r="T11" t="n">
         <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X11" t="n">
         <v>3.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2392,13 +2459,13 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK11" t="n">
         <v>27</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>25</v>
       </c>
       <c r="AL11" t="n">
         <v>10</v>
@@ -2410,43 +2477,43 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ11" t="n">
         <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT11" t="n">
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ11" t="n">
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -2559,10 +2626,10 @@
         <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AE12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12" t="n">
         <v>22</v>
@@ -2595,7 +2662,7 @@
         <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2610,25 +2677,25 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY12" t="n">
         <v>23</v>
       </c>
-      <c r="AW12" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>24</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -2663,67 +2730,67 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" t="n">
         <v>30</v>
       </c>
       <c r="G13" t="n">
-        <v>0.231</v>
+        <v>0.211</v>
       </c>
       <c r="H13" t="n">
         <v>48.8</v>
       </c>
       <c r="I13" t="n">
-        <v>35.3</v>
+        <v>35.2</v>
       </c>
       <c r="J13" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.428</v>
+        <v>0.425</v>
       </c>
       <c r="L13" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="M13" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N13" t="n">
         <v>0.314</v>
       </c>
       <c r="O13" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R13" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T13" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V13" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>7.1</v>
       </c>
       <c r="X13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
@@ -2735,13 +2802,13 @@
         <v>19.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.2</v>
+        <v>93</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.1</v>
+        <v>-7.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2768,7 +2835,7 @@
         <v>24</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="n">
         <v>30</v>
@@ -2777,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>25</v>
@@ -2789,10 +2856,10 @@
         <v>18</v>
       </c>
       <c r="AT13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV13" t="n">
         <v>19</v>
@@ -2804,13 +2871,13 @@
         <v>2</v>
       </c>
       <c r="AY13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.789</v>
+        <v>0.795</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,7 +2930,7 @@
         <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
@@ -2872,31 +2939,31 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="O14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
@@ -2905,28 +2972,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2953,16 +3020,16 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
@@ -2974,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -2983,7 +3050,7 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,16 +3184,16 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ15" t="n">
         <v>27</v>
       </c>
       <c r="AK15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL15" t="n">
         <v>28</v>
@@ -3147,7 +3214,7 @@
         <v>22</v>
       </c>
       <c r="AR15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
         <v>28</v>
@@ -3168,7 +3235,7 @@
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3177,7 +3244,7 @@
         <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC15" t="n">
         <v>26</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
         <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G16" t="n">
-        <v>0.538</v>
+        <v>0.553</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,10 +3294,10 @@
         <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>81.09999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L16" t="n">
         <v>6.8</v>
@@ -3239,67 +3306,67 @@
         <v>19.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="P16" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.738</v>
+        <v>0.741</v>
       </c>
       <c r="R16" t="n">
         <v>10.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T16" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U16" t="n">
         <v>19.9</v>
       </c>
       <c r="V16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y16" t="n">
         <v>4.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.5</v>
+        <v>96.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
       </c>
       <c r="AF16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI16" t="n">
         <v>19</v>
@@ -3308,46 +3375,46 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>14</v>
       </c>
       <c r="AM16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN16" t="n">
         <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR16" t="n">
         <v>17</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU16" t="n">
         <v>25</v>
       </c>
       <c r="AV16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3356,7 +3423,7 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3406,34 +3473,34 @@
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.5</v>
+        <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.448</v>
       </c>
       <c r="L17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M17" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="N17" t="n">
         <v>0.347</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.1</v>
+        <v>24.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
         <v>29.5</v>
@@ -3445,28 +3512,28 @@
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="AA17" t="n">
         <v>22.7</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,7 +3542,7 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
@@ -3484,13 +3551,13 @@
         <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ17" t="n">
         <v>9</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3502,22 +3569,22 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR17" t="n">
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU17" t="n">
         <v>12</v>
@@ -3526,22 +3593,22 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
         <v>14</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-3.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
@@ -3663,10 +3730,10 @@
         <v>24</v>
       </c>
       <c r="AH18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>6</v>
@@ -3678,16 +3745,16 @@
         <v>21</v>
       </c>
       <c r="AM18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
         <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
         <v>20</v>
@@ -3699,10 +3766,10 @@
         <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3755,34 +3822,34 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
         <v>19</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" t="n">
-        <v>0.463</v>
+        <v>0.475</v>
       </c>
       <c r="H19" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I19" t="n">
-        <v>35.4</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N19" t="n">
         <v>0.376</v>
@@ -3791,52 +3858,52 @@
         <v>20.3</v>
       </c>
       <c r="P19" t="n">
-        <v>26</v>
+        <v>25.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.78</v>
+        <v>0.783</v>
       </c>
       <c r="R19" t="n">
         <v>11.3</v>
       </c>
       <c r="S19" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U19" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V19" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W19" t="n">
         <v>6.8</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.8</v>
+        <v>99.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-3</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>17</v>
@@ -3845,25 +3912,25 @@
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL19" t="n">
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
@@ -3872,7 +3939,7 @@
         <v>8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3881,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU19" t="n">
         <v>29</v>
@@ -3890,25 +3957,25 @@
         <v>12</v>
       </c>
       <c r="AW19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ19" t="n">
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>13</v>
       </c>
       <c r="BC19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F20" t="n">
         <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>0.649</v>
+        <v>0.639</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
@@ -3955,70 +4022,70 @@
         <v>34.9</v>
       </c>
       <c r="J20" t="n">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="M20" t="n">
-        <v>19.1</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.383</v>
+        <v>0.388</v>
       </c>
       <c r="O20" t="n">
         <v>18.4</v>
       </c>
       <c r="P20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S20" t="n">
         <v>29.3</v>
       </c>
       <c r="T20" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="U20" t="n">
         <v>19.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="W20" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="X20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.1</v>
+        <v>21.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>95.59999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="AC20" t="n">
         <v>3.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4030,7 +4097,7 @@
         <v>30</v>
       </c>
       <c r="AI20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ20" t="n">
         <v>28</v>
@@ -4039,31 +4106,31 @@
         <v>13</v>
       </c>
       <c r="AL20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS20" t="n">
         <v>26</v>
       </c>
       <c r="AT20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU20" t="n">
         <v>26</v>
@@ -4072,25 +4139,25 @@
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ20" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA20" t="n">
         <v>13</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>15</v>
       </c>
       <c r="BB20" t="n">
         <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E21" t="n">
         <v>15</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" t="n">
-        <v>0.385</v>
+        <v>0.395</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.4</v>
+        <v>37.5</v>
       </c>
       <c r="J21" t="n">
-        <v>86.2</v>
+        <v>86.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L21" t="n">
         <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.358</v>
+        <v>0.356</v>
       </c>
       <c r="O21" t="n">
         <v>17.7</v>
       </c>
       <c r="P21" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.801</v>
+        <v>0.799</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="S21" t="n">
         <v>31.2</v>
       </c>
       <c r="T21" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U21" t="n">
         <v>21.6</v>
       </c>
       <c r="V21" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W21" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X21" t="n">
         <v>2.4</v>
@@ -4191,25 +4258,25 @@
         <v>18.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.9</v>
+        <v>103.1</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.5</v>
+        <v>-3.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
         <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4236,7 +4303,7 @@
         <v>27</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>15</v>
@@ -4248,7 +4315,7 @@
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4449,7 @@
         <v>2</v>
       </c>
       <c r="AE22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF22" t="n">
         <v>30</v>
@@ -4391,7 +4458,7 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>16</v>
@@ -4430,13 +4497,13 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -4445,10 +4512,10 @@
         <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F23" t="n">
         <v>8</v>
       </c>
       <c r="G23" t="n">
-        <v>0.805</v>
+        <v>0.8</v>
       </c>
       <c r="H23" t="n">
         <v>48.1</v>
@@ -4501,7 +4568,7 @@
         <v>36.3</v>
       </c>
       <c r="J23" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="K23" t="n">
         <v>0.461</v>
@@ -4510,34 +4577,34 @@
         <v>10.5</v>
       </c>
       <c r="M23" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
       <c r="O23" t="n">
         <v>19.1</v>
       </c>
       <c r="P23" t="n">
-        <v>26.6</v>
+        <v>26.5</v>
       </c>
       <c r="Q23" t="n">
         <v>0.719</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
         <v>42.9</v>
       </c>
       <c r="U23" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="V23" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="W23" t="n">
         <v>7.4</v>
@@ -4552,16 +4619,16 @@
         <v>20.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.3</v>
+        <v>102.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4591,10 +4658,10 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4612,13 +4679,13 @@
         <v>5</v>
       </c>
       <c r="AU23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW23" t="n">
         <v>13</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>12</v>
       </c>
       <c r="AX23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -4665,46 +4732,46 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F24" t="n">
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
       </c>
       <c r="I24" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J24" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
       </c>
       <c r="M24" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="N24" t="n">
-        <v>0.331</v>
+        <v>0.329</v>
       </c>
       <c r="O24" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P24" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.742</v>
+        <v>0.747</v>
       </c>
       <c r="R24" t="n">
         <v>12.7</v>
@@ -4713,22 +4780,22 @@
         <v>30.1</v>
       </c>
       <c r="T24" t="n">
-        <v>42.8</v>
+        <v>42.7</v>
       </c>
       <c r="U24" t="n">
         <v>20.6</v>
       </c>
       <c r="V24" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W24" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="X24" t="n">
         <v>5.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z24" t="n">
         <v>20.3</v>
@@ -4737,16 +4804,16 @@
         <v>20.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF24" t="n">
         <v>16</v>
@@ -4755,16 +4822,16 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4788,16 +4855,16 @@
         <v>2</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT24" t="n">
         <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
@@ -4812,7 +4879,7 @@
         <v>9</v>
       </c>
       <c r="BA24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB24" t="n">
         <v>23</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4955,7 +5022,7 @@
         <v>16</v>
       </c>
       <c r="AN25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
         <v>6</v>
@@ -4964,10 +5031,10 @@
         <v>6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
         <v>7</v>
@@ -4976,7 +5043,7 @@
         <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
         <v>29</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -5041,34 +5108,34 @@
         <v>0.615</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>35.8</v>
       </c>
       <c r="J26" t="n">
         <v>78.59999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M26" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.385</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.775</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
@@ -5080,37 +5147,37 @@
         <v>40.6</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF26" t="n">
         <v>8</v>
@@ -5119,16 +5186,16 @@
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,13 +5207,13 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5164,25 +5231,25 @@
         <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
       </c>
       <c r="AZ26" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA26" t="n">
         <v>14</v>
       </c>
-      <c r="BA26" t="n">
-        <v>12</v>
-      </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5368,7 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI27" t="n">
         <v>18</v>
@@ -5310,7 +5377,7 @@
         <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5328,31 +5395,31 @@
         <v>12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS27" t="n">
         <v>25</v>
       </c>
       <c r="AT27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
       </c>
       <c r="AW27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
       </c>
       <c r="AY27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ27" t="n">
         <v>28</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F28" t="n">
         <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.667</v>
+        <v>0.658</v>
       </c>
       <c r="H28" t="n">
         <v>48.8</v>
       </c>
       <c r="I28" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J28" t="n">
-        <v>79.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.466</v>
+        <v>0.468</v>
       </c>
       <c r="L28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.401</v>
+        <v>0.404</v>
       </c>
       <c r="O28" t="n">
         <v>14.8</v>
@@ -5432,22 +5499,22 @@
         <v>19.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.76</v>
+        <v>0.759</v>
       </c>
       <c r="R28" t="n">
         <v>8.4</v>
       </c>
       <c r="S28" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T28" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="U28" t="n">
         <v>21.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W28" t="n">
         <v>5.6</v>
@@ -5462,16 +5529,16 @@
         <v>18.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="AB28" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="AC28" t="n">
         <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5480,13 +5547,13 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH28" t="n">
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
@@ -5501,7 +5568,7 @@
         <v>5</v>
       </c>
       <c r="AN28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5519,7 +5586,7 @@
         <v>8</v>
       </c>
       <c r="AT28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
@@ -5531,7 +5598,7 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
         <v>7</v>
@@ -5546,7 +5613,7 @@
         <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -5665,31 +5732,31 @@
         <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI29" t="n">
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM29" t="n">
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5713,7 +5780,7 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -5757,58 +5824,58 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
         <v>24</v>
       </c>
       <c r="F30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>0.585</v>
+        <v>0.6</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J30" t="n">
-        <v>79.7</v>
+        <v>79.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="M30" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="N30" t="n">
-        <v>0.343</v>
+        <v>0.34</v>
       </c>
       <c r="O30" t="n">
         <v>21.3</v>
       </c>
       <c r="P30" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.773</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T30" t="n">
-        <v>41.3</v>
+        <v>41.6</v>
       </c>
       <c r="U30" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="V30" t="n">
         <v>15.3</v>
@@ -5820,34 +5887,34 @@
         <v>4.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z30" t="n">
         <v>22.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>101.8</v>
+        <v>101.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5868,19 +5935,19 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5892,25 +5959,25 @@
         <v>22</v>
       </c>
       <c r="AW30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
         <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>25</v>
       </c>
       <c r="BA30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
@@ -6017,10 +6084,10 @@
         <v>-6.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF31" t="n">
         <v>28</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI31" t="n">
         <v>20</v>
@@ -6041,7 +6108,7 @@
         <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM31" t="n">
         <v>23</v>
@@ -6068,22 +6135,22 @@
         <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AY31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-17-2008-09</t>
+          <t>2009-01-17</t>
         </is>
       </c>
     </row>
